--- a/20_設計書/化学物質申請完了画面.xlsx
+++ b/20_設計書/化学物質申請完了画面.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMA1040\Documents\古竹作成\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA46AAD-2437-425C-855C-AE72659586CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022D8386-FC65-4AA2-933B-59F944F0A978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29940" yWindow="1140" windowWidth="16245" windowHeight="10095" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -182,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="104">
   <si>
     <t>HRS殿</t>
     <rPh sb="3" eb="4">
@@ -860,22 +860,6 @@
     <phoneticPr fontId="54"/>
   </si>
   <si>
-    <t>リンクを押下すると「化学物質データ」画面に遷移する</t>
-    <rPh sb="4" eb="6">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="10" eb="14">
-      <t>カガクブッシツ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="54"/>
-  </si>
-  <si>
     <t>・メール内容の表記を見やすいように変更
 ・共通ヘッダーを追加。</t>
     <rPh sb="4" eb="6">
@@ -988,6 +972,34 @@
       <t>ショウメイショ</t>
     </rPh>
     <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>ホーム画面: ホーム (リンクなし)</t>
+    <phoneticPr fontId="54"/>
+  </si>
+  <si>
+    <t>「画面項目」シート</t>
+    <rPh sb="1" eb="5">
+      <t>ガメンコウモク</t>
+    </rPh>
+    <phoneticPr fontId="50"/>
+  </si>
+  <si>
+    <t>課題リストの回答をもとに修正</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="50"/>
+  </si>
+  <si>
+    <t>dr1.5</t>
+    <phoneticPr fontId="50"/>
   </si>
 </sst>
 </file>
@@ -5893,7 +5905,7 @@
     <row r="22" spans="2:8" ht="14.25" customHeight="1">
       <c r="B22" s="121" t="str">
         <f ca="1">TEXT(変更来歴!AT2,"yyyy年 mm月 dd日") &amp; " " &amp; 変更来歴!AT3</f>
-        <v>2026年 06月 11日 dr1.4</v>
+        <v>2026年 06月 17日 dr1.5</v>
       </c>
       <c r="C22" s="122"/>
       <c r="D22" s="122"/>
@@ -6910,7 +6922,7 @@
     </row>
     <row r="2" spans="1:53">
       <c r="A2" s="149" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B2" s="149"/>
       <c r="C2" s="149"/>
@@ -6926,7 +6938,7 @@
       <c r="K2" s="150"/>
       <c r="L2" s="150"/>
       <c r="M2" s="151" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N2" s="152"/>
       <c r="O2" s="152"/>
@@ -6967,7 +6979,7 @@
       <c r="AR2" s="154"/>
       <c r="AS2" s="154"/>
       <c r="AT2" s="157">
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="AU2" s="157"/>
       <c r="AV2" s="157"/>
@@ -7037,7 +7049,7 @@
       <c r="AS3" s="154"/>
       <c r="AT3" s="170" t="str">
         <f ca="1">INDIRECT("A" &amp; COUNTA(A7:A39) + 6)</f>
-        <v>dr1.4</v>
+        <v>dr1.5</v>
       </c>
       <c r="AU3" s="170"/>
       <c r="AV3" s="170"/>
@@ -7127,7 +7139,7 @@
       <c r="O6" s="156"/>
       <c r="P6" s="156"/>
       <c r="Q6" s="156" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R6" s="156"/>
       <c r="S6" s="156"/>
@@ -7243,7 +7255,7 @@
       </c>
       <c r="B8" s="144"/>
       <c r="C8" s="129" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8" s="129"/>
       <c r="E8" s="129"/>
@@ -7259,7 +7271,7 @@
       <c r="O8" s="129"/>
       <c r="P8" s="129"/>
       <c r="Q8" s="140" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R8" s="141"/>
       <c r="S8" s="141"/>
@@ -7308,7 +7320,7 @@
       </c>
       <c r="B9" s="144"/>
       <c r="C9" s="129" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D9" s="129"/>
       <c r="E9" s="129"/>
@@ -7389,7 +7401,7 @@
       <c r="O10" s="129"/>
       <c r="P10" s="129"/>
       <c r="Q10" s="130" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R10" s="129"/>
       <c r="S10" s="129"/>
@@ -7438,7 +7450,7 @@
       </c>
       <c r="B11" s="144"/>
       <c r="C11" s="130" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D11" s="130"/>
       <c r="E11" s="130"/>
@@ -7454,7 +7466,7 @@
       <c r="O11" s="130"/>
       <c r="P11" s="130"/>
       <c r="Q11" s="130" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R11" s="129"/>
       <c r="S11" s="129"/>
@@ -7498,9 +7510,13 @@
       <c r="BA11" s="129"/>
     </row>
     <row r="12" spans="1:53">
-      <c r="A12" s="128"/>
-      <c r="B12" s="128"/>
-      <c r="C12" s="129"/>
+      <c r="A12" s="143" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="144"/>
+      <c r="C12" s="129" t="s">
+        <v>101</v>
+      </c>
       <c r="D12" s="129"/>
       <c r="E12" s="129"/>
       <c r="F12" s="129"/>
@@ -7514,7 +7530,9 @@
       <c r="N12" s="129"/>
       <c r="O12" s="129"/>
       <c r="P12" s="129"/>
-      <c r="Q12" s="129"/>
+      <c r="Q12" s="129" t="s">
+        <v>102</v>
+      </c>
       <c r="R12" s="129"/>
       <c r="S12" s="129"/>
       <c r="T12" s="129"/>
@@ -7535,11 +7553,15 @@
       <c r="AI12" s="129"/>
       <c r="AJ12" s="129"/>
       <c r="AK12" s="129"/>
-      <c r="AL12" s="127"/>
+      <c r="AL12" s="127">
+        <v>46190</v>
+      </c>
       <c r="AM12" s="128"/>
       <c r="AN12" s="128"/>
       <c r="AO12" s="128"/>
-      <c r="AP12" s="129"/>
+      <c r="AP12" s="129" t="s">
+        <v>58</v>
+      </c>
       <c r="AQ12" s="129"/>
       <c r="AR12" s="129"/>
       <c r="AS12" s="129"/>
@@ -9164,7 +9186,7 @@
       <c r="AU2" s="154"/>
       <c r="AV2" s="157">
         <f ca="1">INDIRECT("変更来歴!AL" &amp; COUNTA(変更来歴!AL7:'変更来歴'!AL39) + 6)</f>
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="AW2" s="170"/>
       <c r="AX2" s="170"/>
@@ -9216,7 +9238,7 @@
       <c r="Z3" s="150"/>
       <c r="AA3" s="166" t="str">
         <f ca="1">MID(CELL("filename"),FIND("]",CELL("filename"))+1,LEN(CELL("filename"))) &amp; "画面"</f>
-        <v>変更来歴画面</v>
+        <v>表紙画面</v>
       </c>
       <c r="AB3" s="166"/>
       <c r="AC3" s="166"/>
@@ -9242,7 +9264,7 @@
       <c r="AU3" s="154"/>
       <c r="AV3" s="170" t="str">
         <f ca="1">INDIRECT("変更来歴!A" &amp; COUNTA(変更来歴!A7:'変更来歴'!A39) + 6)</f>
-        <v>dr1.4</v>
+        <v>dr1.5</v>
       </c>
       <c r="AW3" s="170"/>
       <c r="AX3" s="170"/>
@@ -9256,7 +9278,7 @@
     <row r="5" spans="1:72" ht="13.5" customHeight="1">
       <c r="A5" s="174" t="str">
         <f ca="1">"画面レイアウト"&amp;"("&amp;MID(CELL("filename"),FIND("]",CELL("filename"))+1,LEN(CELL("filename")))&amp;")"</f>
-        <v>画面レイアウト(変更来歴)</v>
+        <v>画面レイアウト(表紙)</v>
       </c>
       <c r="B5" s="175"/>
       <c r="C5" s="175"/>
@@ -23042,7 +23064,7 @@
       <c r="AJ8" s="205"/>
       <c r="AK8" s="206"/>
       <c r="AL8" s="225" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="AM8" s="226"/>
       <c r="AN8" s="226"/>
@@ -23190,7 +23212,7 @@
       <c r="Z10" s="242"/>
       <c r="AA10" s="243"/>
       <c r="AB10" s="204" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AC10" s="205"/>
       <c r="AD10" s="205"/>
@@ -23237,7 +23259,7 @@
       <c r="BS10" s="242"/>
       <c r="BT10" s="245"/>
     </row>
-    <row r="11" spans="1:72" ht="30.75" customHeight="1">
+    <row r="11" spans="1:72">
       <c r="A11" s="194">
         <v>2.2000000000000002</v>
       </c>
